--- a/output/pdf_financials_xlsx/AVL.xlsx
+++ b/output/pdf_financials_xlsx/AVL.xlsx
@@ -6309,22 +6309,22 @@
         <v>3.054653</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>7.967053</v>
+        <v>4.055202</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.670248</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.655732</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.66108</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.863018</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.020968</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
@@ -6332,31 +6332,31 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.258213</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.32943</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.330037</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.336481</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.33638</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.358451</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.37124</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.920753</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>5.215436</v>
       </c>
     </row>
     <row r="93">
@@ -7918,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-16.860576</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-28.491378</v>
@@ -11544,7 +11544,11 @@
           <t>Reserve for Warrants (note 13c)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -13614,7 +13618,11 @@
           <t>Reserve for Warrants (note 15c)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -15260,7 +15268,11 @@
           <t>Reserve for Warrants (note 14c)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -16690,7 +16702,11 @@
           <t>Reserve for Warrants (note 12c)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -18450,7 +18466,11 @@
           <t>Reserve for Warrants (note 11c)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -19182,7 +19202,11 @@
           <t>Reserve for Warrants (note 10c)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -19804,7 +19828,11 @@
           <t>Reserve for Warrants (note 8)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -28080,7 +28108,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AVL.xlsx
+++ b/output/pdf_financials_xlsx/AVL.xlsx
@@ -8339,10 +8339,10 @@
         </is>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.245405</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.191822</v>
       </c>
     </row>
     <row r="125">
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.245405</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.191822</v>
       </c>
     </row>
     <row r="126">
@@ -22786,7 +22786,11 @@
           <t>Net lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
